--- a/Luban/Config/Datas/Levels/L23/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L23/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L23 W1/25; N=53; EHP=342.804000; normal:17x26,normal:18x27</t>
+          <t>L23 W1/25; N=53; EHP=915.367587; normal:17x26,normal:18x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L23 W2/25; N=59; EHP=399.585925; normal:17x30,normal:18x29</t>
+          <t>L23 W2/25; N=59; EHP=1066.988729; normal:17x30,normal:18x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10019276,10019278,10048792,10019276,10019278,10048792,10019276,10019278,10048793,10019276,10019278,10048794,10019276,10019278,10048794,10019276,10019278,10048795,10019276,10019278,10048795,10019276,10019278,10048796,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277</t>
+          <t>10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019278,10019276,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277,10019277</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L23 W3/25; N=65; EHP=487.014528; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x19,normal:18x20,swarm:84x18</t>
+          <t>L23 W3/25; N=65; EHP=1405.820389; normal:17x19,normal:18x28,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10019279,10019281,10048797,10019279,10019281,10048797,10019279,10019281,10048798,10019279,10019281,10048798,10019279,10019281,10048799,10019279,10019281,10048800,10019279,10019281,10048800,10019279,10019281,10048801,10019279,10019281,10048801,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019279,10019279,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280</t>
+          <t>10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019281,10019279,10019279,10019279,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019280,10019279,10019279,10019279,10019279,10019279,10019279,10019279,10019279,10019279</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L23 W4/25; N=71; EHP=612.564229; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x22,normal:18x21,swarm:84x19</t>
+          <t>L23 W4/25; N=71; EHP=1771.998655; normal:17x31,normal:18x21,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10019282,10019285,10048802,10019284,10019282,10019285,10048803,10019284,10019282,10019285,10048803,10019284,10019282,10019285,10048804,10019286,10019282,10019285,10048804,10019286,10019282,10019285,10048805,10019286,10019282,10019285,10048805,10019286,10019282,10019285,10048806,10019287,10019282,10019285,10048806,10019287,10019282,10019285,10019287,10019282,10019285,10019287,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019283,10019285,10019283,10019285,10019283,10019285,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283</t>
+          <t>10019282,10048802,10048802,10019284,10019282,10048803,10048803,10019284,10019282,10048803,10048803,10019284,10019282,10048804,10048804,10019286,10019282,10048804,10048804,10019286,10019282,10048805,10048805,10019286,10019282,10048805,10048805,10019286,10019282,10048806,10048806,10019287,10019282,10048806,10048806,10019287,10019282,10019285,10019287,10019282,10019285,10019287,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019282,10019285,10019283,10019285,10019283,10019285,10019283,10019285,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283,10019283</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L23 W5/25; N=77; EHP=1145.000000; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x18,medium:83x3,swarm:84x21,medium:108x4,medium:123x4</t>
+          <t>L23 W5/25; N=77; EHP=3095.426843; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x3,medium:108x4,medium:123x4,normal:17x18,normal:18x18,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10019291,10019297,10019293,10048807,10019296,10019291,10019297,10019293,10048807,10019296,10019291,10019297,10019294,10019288,10019296,10019291,10019297,10019294,10019288,10019296,10019291,10019297,10019295,10048808,10019299,10019291,10019297,10019295,10048808,10019299,10019291,10019297,10019298,10019289,10019299,10019291,10019297,10019298,10019289,10019299,10019291,10019297,10019298,10019290,10019300,10019291,10019297,10019290,10019300,10019291,10019297,10019300,10019291,10019297,10019300,10019291,10019297,10019291,10019297,10019291,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019292,10019292,10019292,10019292,10019292</t>
+          <t>10019291,10048807,10019293,10048807,10019296,10019291,10048807,10019293,10048807,10019296,10019291,10019288,10019294,10019288,10019296,10019291,10019288,10019294,10019288,10019296,10019291,10048808,10019295,10048808,10019299,10019291,10048808,10019295,10048808,10019299,10019291,10019289,10019298,10019289,10019299,10019291,10019289,10019298,10019289,10019299,10019291,10019290,10019298,10019290,10019300,10019291,10019290,10019290,10019300,10019291,10019297,10019300,10019291,10019297,10019300,10019291,10019297,10019291,10019297,10019291,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019297,10019292,10019292,10019292,10019292,10019292,10019292</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L23 W6/25; N=83; EHP=1168.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x14,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x23,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L23 W6/25; N=83; EHP=3159.604760; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10019304,10019310,10019306,10048809,10019309,10019304,10019310,10019306,10048809,10019309,10019304,10019310,10019307,10019301,10019309,10019304,10019310,10019307,10019301,10019309,10019304,10019310,10019307,10048810,10019309,10019304,10019310,10019308,10048810,10019312,10019304,10019310,10019308,10019302,10019312,10019304,10019310,10019308,10019302,10019312,10019304,10019310,10019311,10019303,10019312,10019304,10019310,10019311,10019303,10019313,10019304,10019310,10019303,10019313,10019304,10019310,10019313,10019304,10019310,10019313,10019304,10019310,10019304,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019305,10019305,10019305,10019305,10019305,10019305</t>
+          <t>10019304,10048809,10019306,10048809,10019309,10019304,10048809,10019306,10048809,10019309,10019304,10019301,10019307,10019301,10019309,10019304,10019301,10019307,10019301,10019309,10019304,10048810,10019307,10048810,10019309,10019304,10048810,10019308,10048810,10019312,10019304,10019302,10019308,10019302,10019312,10019304,10019302,10019308,10019302,10019312,10019304,10019303,10019311,10019303,10019312,10019304,10019303,10019311,10019303,10019313,10019304,10019303,10019303,10019313,10019304,10019310,10019313,10019304,10019310,10019313,10019304,10019310,10019304,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019310,10019305,10019305,10019305,10019305,10019305,10019305,10019305</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L23 W7/25; N=89; EHP=1310.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x15,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x5,swarm:84x24,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L23 W7/25; N=89; EHP=3544.848013; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x5,medium:108x4,medium:123x4,normal:17x15,normal:18x16,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10019317,10019323,10019319,10048811,10019322,10019317,10019323,10019319,10048811,10019322,10019317,10019323,10019319,10019314,10019322,10019317,10019323,10019320,10019314,10019322,10019317,10019323,10019320,10048812,10019325,10019317,10019323,10019321,10048812,10019325,10019317,10019323,10019321,10048812,10019325,10019317,10019323,10019321,10019315,10019325,10019317,10019323,10019324,10019315,10019325,10019317,10019323,10019324,10019316,10019326,10019317,10019323,10019324,10019316,10019326,10019317,10019323,10019326,10019317,10019323,10019326,10019317,10019323,10019326,10019317,10019323,10019317,10019323,10019317,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019318,10019318,10019318,10019318,10019318,10019318</t>
+          <t>10019317,10048811,10019319,10048811,10019322,10019317,10048811,10019319,10048811,10019322,10019317,10019314,10019319,10019314,10019322,10019317,10019314,10019320,10019314,10019322,10019317,10048812,10019320,10048812,10019325,10019317,10048812,10019321,10048812,10019325,10019317,10048812,10019321,10048812,10019325,10019317,10019315,10019321,10019315,10019325,10019317,10019315,10019324,10019315,10019325,10019317,10019316,10019324,10019316,10019326,10019317,10019316,10019324,10019316,10019326,10019317,10019323,10019326,10019317,10019323,10019326,10019317,10019323,10019326,10019317,10019323,10019317,10019323,10019317,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019323,10019318,10019318,10019318,10019318,10019318,10019318,10019318</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L23 W8/25; N=95; EHP=1683.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x17,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x26,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L23 W8/25; N=95; EHP=4550.182304; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x5,normal:17x17,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10019330,10019336,10019332,10048813,10019335,10019330,10019336,10019332,10048813,10019335,10019330,10019336,10019332,10048813,10019335,10019330,10019336,10019333,10019327,10019335,10019330,10019336,10019333,10019327,10019335,10019330,10019336,10019333,10048814,10019338,10019330,10019336,10019334,10048814,10019338,10019330,10019336,10019334,10019328,10019338,10019330,10019336,10019334,10019328,10019338,10019330,10019336,10019337,10019328,10019338,10019330,10019336,10019337,10019329,10019339,10019330,10019336,10019337,10019329,10019339,10019330,10019336,10019339,10019330,10019336,10019339,10019330,10019336,10019339,10019330,10019336,10019330,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019331,10019331,10019331,10019331,10019331</t>
+          <t>10019330,10048813,10019332,10048813,10019335,10019330,10048813,10019332,10048813,10019335,10019330,10048813,10019332,10048813,10019335,10019330,10019327,10019333,10019327,10019335,10019330,10019327,10019333,10019327,10019335,10019330,10048814,10019333,10048814,10019338,10019330,10048814,10019334,10048814,10019338,10019330,10019328,10019334,10019328,10019338,10019330,10019328,10019334,10019328,10019338,10019330,10019328,10019337,10019328,10019338,10019330,10019329,10019337,10019329,10019339,10019330,10019329,10019337,10019329,10019339,10019330,10019336,10019339,10019330,10019336,10019339,10019330,10019336,10019339,10019330,10019336,10019330,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019336,10019331,10019331,10019331,10019331,10019331,10019331</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L23 W9/25; N=101; EHP=2148.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L23 W9/25; N=101; EHP=5809.437597; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x17,normal:18x17,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10019343,10019349,10019345,10048815,10019348,10019343,10019349,10019345,10048815,10019348,10019343,10019349,10019345,10019340,10019348,10019343,10019349,10019346,10019340,10019348,10019343,10019349,10019346,10019340,10019348,10019343,10019349,10019346,10048816,10019348,10019343,10019349,10019347,10048816,10019351,10019343,10019349,10019347,10019341,10019351,10019343,10019349,10019347,10019341,10019351,10019343,10019349,10019350,10019341,10019351,10019343,10019349,10019350,10019342,10019351,10019343,10019349,10019350,10019342,10019352,10019343,10019349,10019342,10019352,10019343,10019349,10019352,10019343,10019349,10019352,10019343,10019349,10019352,10019343,10019349,10019343,10019349,10019343,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019344,10019344,10019344,10019344,10019344,10019344,10019344</t>
+          <t>10019343,10048815,10019345,10048815,10019348,10019343,10048815,10019345,10048815,10019348,10019343,10019340,10019345,10019340,10019348,10019343,10019340,10019346,10019340,10019348,10019343,10019340,10019346,10019340,10019348,10019343,10048816,10019346,10048816,10019348,10019343,10048816,10019347,10048816,10019351,10019343,10019341,10019347,10019341,10019351,10019343,10019341,10019347,10019341,10019351,10019343,10019341,10019350,10019341,10019351,10019343,10019342,10019350,10019342,10019351,10019343,10019342,10019350,10019342,10019352,10019343,10019342,10019342,10019352,10019343,10019349,10019352,10019343,10019349,10019352,10019343,10019349,10019352,10019343,10019349,10019343,10019349,10019343,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019349,10019344,10019344,10019344,10019344,10019344,10019344,10019344,10019344</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L23 W10/25; N=107; EHP=3958.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x19,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x6,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L23 W10/25; N=107; EHP=10707.436251; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x6,medium:108x5,medium:123x5,normal:17x19,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10019353,10019363,10019355,10048817,10019362,10019356,10019353,10019363,10019355,10048817,10019362,10019356,10019353,10019363,10019355,10048817,10019362,10019357,10019353,10019363,10019358,10048818,10019362,10019357,10019353,10019363,10019358,10048818,10019362,10019360,10019353,10019363,10019358,10048818,10019366,10019361,10019353,10019363,10019358,10048819,10019366,10045240,10019353,10019363,10019359,10048819,10019366,10019364,10019353,10019363,10019359,10048819,10019366,10019364,10019353,10019363,10019359,10048820,10019366,10045241,10019353,10019363,10019365,10048820,10019367,10019368,10019353,10019363,10019365,10048821,10019367,10019353,10019363,10019365,10048821,10019367,10019353,10019363,10048821,10019367,10019354,10019363,10019367,10019354,10019363,10019367,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019363,10019363,10019363</t>
+          <t>10019353,10048817,10019355,10048817,10019362,10019356,10019353,10048817,10019355,10048817,10019362,10019356,10019353,10048817,10019355,10048817,10019362,10019357,10019353,10048818,10019358,10048818,10019362,10019357,10019353,10048818,10019358,10048818,10019362,10019360,10019353,10048818,10019358,10048818,10019366,10019361,10019353,10048819,10019358,10048819,10019366,10045240,10019353,10048819,10019359,10048819,10019366,10019364,10019353,10048819,10019359,10048819,10019366,10019364,10019353,10048820,10019359,10048820,10019366,10045241,10019353,10048820,10019365,10048820,10019367,10019368,10019353,10048821,10019365,10048821,10019367,10019353,10048821,10019365,10048821,10019367,10019353,10048821,10048821,10019367,10019354,10019363,10019367,10019354,10019363,10019367,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019354,10019363,10019363,10019363,10019363</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L23 W11/25; N=113; EHP=4038.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x1,fast:98x3,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L23 W11/25; N=113; EHP=10911.543725; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10019372,10019382,10019374,10048822,10019381,10019375,10019372,10019382,10019374,10048822,10019381,10019375,10019372,10019382,10019374,10048822,10019381,10019376,10019372,10019382,10019374,10019369,10019381,10019376,10019372,10019382,10019377,10019369,10019381,10019379,10019372,10019382,10019377,10048823,10019381,10019380,10019372,10019382,10019377,10048823,10019385,10045242,10019372,10019382,10019378,10048823,10019385,10045243,10019372,10019382,10019378,10019370,10019385,10019383,10019372,10019382,10019378,10019370,10019385,10019387,10019372,10019382,10019378,10019370,10019385,10019387,10019372,10019382,10019384,10019371,10019385,10019372,10019382,10019384,10019371,10019386,10019372,10019382,10019384,10019371,10019386,10019372,10019382,10019386,10019373,10019382,10019386,10019373,10019382,10019386,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019382,10019382,10019382</t>
+          <t>10019372,10048822,10019374,10048822,10019381,10019375,10019372,10048822,10019374,10048822,10019381,10019375,10019372,10048822,10019374,10048822,10019381,10019376,10019372,10019369,10019374,10019369,10019381,10019376,10019372,10019369,10019377,10019369,10019381,10019379,10019372,10048823,10019377,10048823,10019381,10019380,10019372,10048823,10019377,10048823,10019385,10045242,10019372,10048823,10019378,10048823,10019385,10045243,10019372,10019370,10019378,10019370,10019385,10019383,10019372,10019370,10019378,10019370,10019385,10019387,10019372,10019370,10019378,10019370,10019385,10019387,10019372,10019371,10019384,10019371,10019385,10019372,10019371,10019384,10019371,10019386,10019372,10019371,10019384,10019371,10019386,10019372,10019382,10019386,10019373,10019382,10019386,10019373,10019382,10019386,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019373,10019382,10019382,10019382,10019382</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L23 W12/25; N=119; EHP=4178.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L23 W12/25; N=119; EHP=11283.486353; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x5,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10019391,10019401,10019393,10048824,10019400,10045244,10019391,10019401,10019393,10048824,10019400,10019394,10019391,10019401,10019393,10048824,10019400,10019394,10019391,10019401,10019393,10019388,10019400,10019397,10019391,10019401,10019395,10019388,10019400,10019397,10019391,10019401,10019395,10019388,10019400,10019398,10019391,10019401,10019395,10048825,10019404,10019398,10019391,10019401,10019395,10048825,10019404,10019399,10019391,10019401,10019396,10048825,10019404,10045245,10019391,10019401,10019396,10019389,10019404,10019402,10019391,10019401,10019396,10019389,10019404,10019406,10019391,10019401,10019403,10019389,10019404,10019406,10019391,10019401,10019403,10019390,10019405,10019391,10019401,10019403,10019390,10019405,10019391,10019401,10019403,10019390,10019405,10019392,10019401,10019405,10019392,10019401,10019405,10019392,10019401,10019405,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019401,10019401,10019401,10019401,10019401</t>
+          <t>10019391,10048824,10019393,10048824,10019400,10045244,10019391,10048824,10019393,10048824,10019400,10019394,10019391,10048824,10019393,10048824,10019400,10019394,10019391,10019388,10019393,10019388,10019400,10019397,10019391,10019388,10019395,10019388,10019400,10019397,10019391,10019388,10019395,10019388,10019400,10019398,10019391,10048825,10019395,10048825,10019404,10019398,10019391,10048825,10019395,10048825,10019404,10019399,10019391,10048825,10019396,10048825,10019404,10045245,10019391,10019389,10019396,10019389,10019404,10019402,10019391,10019389,10019396,10019389,10019404,10019406,10019391,10019389,10019403,10019389,10019404,10019406,10019391,10019390,10019403,10019390,10019405,10019391,10019390,10019403,10019390,10019405,10019391,10019390,10019403,10019390,10019405,10019392,10019401,10019405,10019392,10019401,10019405,10019392,10019401,10019405,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019392,10019401,10019401,10019401,10019401,10019401,10019401</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L23 W13/25; N=125; EHP=5096.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L23 W13/25; N=125; EHP=13765.443694; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10019410,10019419,10019412,10048826,10019418,10045246,10019410,10019419,10019412,10048826,10019418,10045247,10019410,10019419,10019412,10048826,10019418,10019415,10019410,10019419,10019413,10048826,10019418,10019415,10019410,10019419,10019413,10019407,10019418,10019416,10019410,10019419,10019413,10019407,10019418,10019416,10019410,10019419,10019413,10019407,10019423,10019417,10019410,10019419,10019414,10048827,10019423,10019417,10019410,10019419,10019414,10048827,10019423,10019420,10019410,10019419,10019414,10048827,10019423,10019421,10019410,10019419,10019414,10019408,10019423,10019421,10019410,10019419,10019422,10019408,10019423,10019425,10019410,10019419,10019422,10019408,10019424,10019425,10019410,10019419,10019422,10019409,10019424,10019410,10019419,10019422,10019409,10019424,10019410,10019419,10019409,10019424,10019411,10019419,10019424,10019411,10019419,10019424,10019411,10019419,10019424,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019419,10019419,10019419,10019419</t>
+          <t>10019410,10048826,10019412,10048826,10019418,10045246,10019410,10048826,10019412,10048826,10019418,10045247,10019410,10048826,10019412,10048826,10019418,10019415,10019410,10048826,10019413,10048826,10019418,10019415,10019410,10019407,10019413,10019407,10019418,10019416,10019410,10019407,10019413,10019407,10019418,10019416,10019410,10019407,10019413,10019407,10019423,10019417,10019410,10048827,10019414,10048827,10019423,10019417,10019410,10048827,10019414,10048827,10019423,10019420,10019410,10048827,10019414,10048827,10019423,10019421,10019410,10019408,10019414,10019408,10019423,10019421,10019410,10019408,10019422,10019408,10019423,10019425,10019410,10019408,10019422,10019408,10019424,10019425,10019410,10019409,10019422,10019409,10019424,10019410,10019409,10019422,10019409,10019424,10019410,10019409,10019409,10019424,10019411,10019419,10019424,10019411,10019419,10019424,10019411,10019419,10019424,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019411,10019419,10019419,10019419,10019419,10019419</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L23 W14/25; N=131; EHP=6147.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L23 W14/25; N=131; EHP=16606.691650; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10019429,10019440,10019431,10048828,10019439,10019432,10019435,10019429,10019440,10019431,10048828,10019439,10045248,10019429,10019440,10019431,10048828,10019439,10019436,10019429,10019440,10019431,10019426,10019439,10019436,10019429,10019440,10019433,10019426,10019439,10019437,10019429,10019440,10019433,10019426,10019439,10019437,10019429,10019440,10019433,10048829,10019439,10019438,10019429,10019440,10019433,10048829,10019444,10019438,10019429,10019440,10019434,10048829,10019444,10019441,10019429,10019440,10019434,10019427,10019444,10019441,10019429,10019440,10019434,10019427,10019444,10019442,10019429,10019440,10019434,10019427,10019444,10019442,10019429,10019440,10019443,10019427,10019444,10045249,10019429,10019440,10019443,10019428,10019444,10019429,10019440,10019443,10019428,10019445,10019429,10019440,10019443,10019428,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019440,10019440,10019440,10019440,10019440</t>
+          <t>10019429,10048828,10019431,10048828,10019439,10019432,10019435,10019429,10048828,10019431,10048828,10019439,10045248,10019429,10048828,10019431,10048828,10019439,10019436,10019429,10019426,10019431,10019426,10019439,10019436,10019429,10019426,10019433,10019426,10019439,10019437,10019429,10019426,10019433,10019426,10019439,10019437,10019429,10048829,10019433,10048829,10019439,10019438,10019429,10048829,10019433,10048829,10019444,10019438,10019429,10048829,10019434,10048829,10019444,10019441,10019429,10019427,10019434,10019427,10019444,10019441,10019429,10019427,10019434,10019427,10019444,10019442,10019429,10019427,10019434,10019427,10019444,10019442,10019429,10019427,10019443,10019427,10019444,10045249,10019429,10019428,10019443,10019428,10019444,10019429,10019428,10019443,10019428,10019445,10019429,10019428,10019443,10019428,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019445,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019430,10019440,10019440,10019440,10019440,10019440,10019440</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L23 W15/25; N=137; EHP=10728.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x1</t>
+          <t>L23 W15/25; N=137; EHP=28960.439108; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10019446,10019456,10019448,10048830,10019455,10019449,10019446,10019456,10019448,10048830,10019455,10019449,10019446,10019456,10019448,10048830,10019455,10019450,10019446,10019456,10019448,10048831,10019455,10019450,10019446,10019456,10019451,10048831,10019455,10019453,10019446,10019456,10019451,10048831,10019455,10019453,10019446,10019456,10019451,10048831,10019455,10045250,10019446,10019456,10019451,10048832,10019460,10019454,10019446,10019456,10019452,10048832,10019460,10019454,10019446,10019456,10019452,10048832,10019460,10019457,10019446,10019456,10019452,10048833,10019460,10019457,10019446,10019456,10019452,10048833,10019460,10019458,10019446,10019456,10019452,10048833,10019460,10019458,10019446,10019456,10019459,10048834,10019460,10019462,10019446,10019456,10019459,10048834,10019461,10019446,10019456,10019459,10048834,10019461,10019446,10019456,10019459,10048834,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019456,10019456,10019456,10019456,10019456,10019456</t>
+          <t>10019446,10048830,10019448,10048830,10019455,10019449,10019446,10048830,10019448,10048830,10019455,10019449,10019446,10048830,10019448,10048830,10019455,10019450,10019446,10048831,10019448,10048831,10019455,10019450,10019446,10048831,10019451,10048831,10019455,10019453,10019446,10048831,10019451,10048831,10019455,10019453,10019446,10048831,10019451,10048831,10019455,10045250,10019446,10048832,10019451,10048832,10019460,10019454,10019446,10048832,10019452,10048832,10019460,10019454,10019446,10048832,10019452,10048832,10019460,10019457,10019446,10048833,10019452,10048833,10019460,10019457,10019446,10048833,10019452,10048833,10019460,10019458,10019446,10048833,10019452,10048833,10019460,10019458,10019446,10048834,10019459,10048834,10019460,10019462,10019446,10048834,10019459,10048834,10019461,10019446,10048834,10019459,10048834,10019461,10019446,10048834,10019459,10048834,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019461,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019447,10019456,10019456,10019456,10019456,10019456,10019456,10019456</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L23 W16/25; N=143; EHP=10943.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L23 W16/25; N=143; EHP=29554.677154; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10019466,10019476,10019468,10048835,10019475,10019469,10019466,10019476,10019468,10048835,10019475,10019469,10019466,10019476,10019468,10048835,10019475,10019470,10019466,10019476,10019468,10048835,10019475,10019470,10019466,10019476,10019468,10019463,10019475,10045251,10019466,10019476,10019471,10019463,10019475,10019473,10019466,10019476,10019471,10019463,10019475,10019474,10019466,10019476,10019471,10048836,10019480,10019474,10019466,10019476,10019471,10048836,10019480,10019477,10019466,10019476,10019472,10048836,10019480,10019477,10019466,10019476,10019472,10048836,10019480,10019478,10019466,10019476,10019472,10019464,10019480,10019478,10019466,10019476,10019472,10019464,10019480,10019482,10019466,10019476,10019479,10019464,10019480,10019482,10019466,10019476,10019479,10019465,10019481,10019466,10019476,10019479,10019465,10019481,10019466,10019476,10019479,10019465,10019481,10019466,10019476,10019465,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019476,10019476,10019476,10019476</t>
+          <t>10019466,10048835,10019468,10048835,10019475,10019469,10019466,10048835,10019468,10048835,10019475,10019469,10019466,10048835,10019468,10048835,10019475,10019470,10019466,10048835,10019468,10048835,10019475,10019470,10019466,10019463,10019468,10019463,10019475,10045251,10019466,10019463,10019471,10019463,10019475,10019473,10019466,10019463,10019471,10019463,10019475,10019474,10019466,10048836,10019471,10048836,10019480,10019474,10019466,10048836,10019471,10048836,10019480,10019477,10019466,10048836,10019472,10048836,10019480,10019477,10019466,10048836,10019472,10048836,10019480,10019478,10019466,10019464,10019472,10019464,10019480,10019478,10019466,10019464,10019472,10019464,10019480,10019482,10019466,10019464,10019479,10019464,10019480,10019482,10019466,10019465,10019479,10019465,10019481,10019466,10019465,10019479,10019465,10019481,10019466,10019465,10019479,10019465,10019481,10019466,10019465,10019465,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019481,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019467,10019476,10019476,10019476,10019476,10019476</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L23 W17/25; N=149; EHP=11162.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L23 W17/25; N=149; EHP=30152.644053; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x19,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10019486,10019497,10019488,10048837,10019496,10019489,10019486,10019497,10019488,10048837,10019496,10019489,10019486,10019497,10019488,10048837,10019496,10019490,10019486,10019497,10019488,10048837,10019496,10019490,10019486,10019497,10019491,10019483,10019496,10019493,10019486,10019497,10019491,10019483,10019496,10019493,10019486,10019497,10019491,10019483,10019496,10019494,10019486,10019497,10019491,10019483,10019496,10019494,10019486,10019497,10019491,10048838,10019500,10019495,10019486,10019497,10019492,10048838,10019500,10019495,10019486,10019497,10019492,10048838,10019500,10019498,10019486,10019497,10019492,10048838,10019500,10019498,10019486,10019497,10019492,10019484,10019500,10045252,10019486,10019497,10019499,10019484,10019500,10019502,10019486,10019497,10019499,10019484,10019500,10019502,10019486,10019497,10019499,10019484,10019500,10019486,10019497,10019499,10019485,10019501,10019486,10019497,10019499,10019485,10019501,10019486,10019497,10019485,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019497,10019497,10019497,10019497,10019497,10019497</t>
+          <t>10019486,10048837,10019488,10048837,10019496,10019489,10019486,10048837,10019488,10048837,10019496,10019489,10019486,10048837,10019488,10048837,10019496,10019490,10019486,10048837,10019488,10048837,10019496,10019490,10019486,10019483,10019491,10019483,10019496,10019493,10019486,10019483,10019491,10019483,10019496,10019493,10019486,10019483,10019491,10019483,10019496,10019494,10019486,10019483,10019491,10019483,10019496,10019494,10019486,10048838,10019491,10048838,10019500,10019495,10019486,10048838,10019492,10048838,10019500,10019495,10019486,10048838,10019492,10048838,10019500,10019498,10019486,10048838,10019492,10048838,10019500,10019498,10019486,10019484,10019492,10019484,10019500,10045252,10019486,10019484,10019499,10019484,10019500,10019502,10019486,10019484,10019499,10019484,10019500,10019502,10019486,10019484,10019499,10019484,10019500,10019486,10019485,10019499,10019485,10019501,10019486,10019485,10019499,10019485,10019501,10019486,10019485,10019485,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019501,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019487,10019497,10019497,10019497,10019497,10019497,10019497,10019497</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L23 W18/25; N=155; EHP=11924.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x19,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x1,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L23 W18/25; N=155; EHP=32215.878082; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10019506,10019516,10019508,10048839,10019515,10019509,10019506,10019516,10019508,10048839,10019515,10019509,10019506,10019516,10019508,10048839,10019515,10019510,10019506,10019516,10019508,10048839,10019515,10019510,10019506,10019516,10019508,10019503,10019515,10019513,10019506,10019516,10019511,10019503,10019515,10019513,10019506,10019516,10019511,10019503,10019515,10019514,10019506,10019516,10019511,10019503,10019515,10019514,10019506,10019516,10019511,10048840,10019520,10045253,10019506,10019516,10019511,10048840,10019520,10045253,10019506,10019516,10019512,10048840,10019520,10019517,10019506,10019516,10019512,10019504,10019520,10019517,10019506,10019516,10019512,10019504,10019520,10019518,10019506,10019516,10019512,10019504,10019520,10019518,10019506,10019516,10019512,10019504,10019520,10019522,10019506,10019516,10019519,10019505,10019520,10019522,10019506,10019516,10019519,10019505,10019521,10019506,10019516,10019519,10019505,10019521,10019506,10019516,10019519,10019505,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019516,10019516,10019516,10019516,10019516,10019516,10019516</t>
+          <t>10019506,10048839,10019508,10048839,10019515,10019509,10019506,10048839,10019508,10048839,10019515,10019509,10019506,10048839,10019508,10048839,10019515,10019510,10019506,10048839,10019508,10048839,10019515,10019510,10019506,10019503,10019508,10019503,10019515,10019513,10019506,10019503,10019511,10019503,10019515,10019513,10019506,10019503,10019511,10019503,10019515,10019514,10019506,10019503,10019511,10019503,10019515,10019514,10019506,10048840,10019511,10048840,10019520,10045253,10019506,10048840,10019511,10048840,10019520,10045253,10019506,10048840,10019512,10048840,10019520,10019517,10019506,10019504,10019512,10019504,10019520,10019517,10019506,10019504,10019512,10019504,10019520,10019518,10019506,10019504,10019512,10019504,10019520,10019518,10019506,10019504,10019512,10019504,10019520,10019522,10019506,10019505,10019519,10019505,10019520,10019522,10019506,10019505,10019519,10019505,10019521,10019506,10019505,10019519,10019505,10019521,10019506,10019505,10019519,10019505,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019521,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019507,10019516,10019516,10019516,10019516,10019516,10019516,10019516,10019516</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L23 W19/25; N=161; EHP=13812.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L23 W19/25; N=161; EHP=37298.533959; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10019526,10019538,10019528,10048841,10019537,10019529,10019533,10019526,10019538,10019528,10048841,10019537,10019529,10019526,10019538,10019528,10048841,10019537,10019530,10019526,10019538,10019528,10048841,10019537,10019530,10019526,10019538,10019528,10019523,10019537,10019534,10019526,10019538,10019531,10019523,10019537,10019534,10019526,10019538,10019531,10019523,10019537,10019535,10019526,10019538,10019531,10019523,10019537,10019535,10019526,10019538,10019531,10048842,10019541,10019536,10019526,10019538,10019531,10048842,10019541,10019536,10019526,10019538,10019532,10048842,10019541,10045254,10019526,10019538,10019532,10048842,10019541,10045254,10019526,10019538,10019532,10019524,10019541,10019539,10019526,10019538,10019532,10019524,10019541,10019539,10019526,10019538,10019532,10019524,10019541,10019543,10019526,10019538,10019540,10019524,10019541,10019543,10019526,10019538,10019540,10019525,10019542,10019526,10019538,10019540,10019525,10019542,10019526,10019538,10019540,10019525,10019542,10019526,10019538,10019540,10019525,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019538,10019538,10019538,10019538,10019538,10019538,10019538</t>
+          <t>10019526,10048841,10019528,10048841,10019537,10019529,10019533,10019526,10048841,10019528,10048841,10019537,10019529,10019526,10048841,10019528,10048841,10019537,10019530,10019526,10048841,10019528,10048841,10019537,10019530,10019526,10019523,10019528,10019523,10019537,10019534,10019526,10019523,10019531,10019523,10019537,10019534,10019526,10019523,10019531,10019523,10019537,10019535,10019526,10019523,10019531,10019523,10019537,10019535,10019526,10048842,10019531,10048842,10019541,10019536,10019526,10048842,10019531,10048842,10019541,10019536,10019526,10048842,10019532,10048842,10019541,10045254,10019526,10048842,10019532,10048842,10019541,10045254,10019526,10019524,10019532,10019524,10019541,10019539,10019526,10019524,10019532,10019524,10019541,10019539,10019526,10019524,10019532,10019524,10019541,10019543,10019526,10019524,10019540,10019524,10019541,10019543,10019526,10019525,10019540,10019525,10019542,10019526,10019525,10019540,10019525,10019542,10019526,10019525,10019540,10019525,10019542,10019526,10019525,10019540,10019525,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019542,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019527,10019538,10019538,10019538,10019538,10019538,10019538,10019538,10019538</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L23 W20/25; N=167; EHP=23184.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L23 W20/25; N=167; EHP=62604.685846; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10019547,10019558,10019549,10048843,10019557,10019550,10019547,10019558,10019549,10048843,10019557,10019550,10019547,10019558,10019549,10048843,10019557,10019551,10019547,10019558,10019549,10048843,10019557,10019551,10019547,10019558,10019549,10019544,10019557,10019551,10019547,10019558,10019552,10019544,10019557,10019554,10019547,10019558,10019552,10019544,10019557,10019554,10019547,10019558,10019552,10019544,10019557,10019555,10019547,10019558,10019552,10019544,10019562,10019555,10019547,10019558,10019552,10048844,10019562,10019556,10019547,10019558,10019553,10048844,10019562,10019556,10019547,10019558,10019553,10048844,10019562,10019559,10019547,10019558,10019553,10048844,10019562,10019559,10019547,10019558,10019553,10019545,10019562,10019560,10019547,10019558,10019553,10019545,10019562,10019560,10019547,10019558,10019561,10019545,10019562,10019564,10019547,10019558,10019561,10019545,10019562,10019564,10019547,10019558,10019561,10019546,10019563,10019547,10019558,10019561,10019546,10019563,10019547,10019558,10019561,10019546,10019563,10019547,10019558,10019546,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019558,10019558,10019558,10019558,10019558,10019558</t>
+          <t>10019547,10048843,10019549,10048843,10019557,10019550,10019547,10048843,10019549,10048843,10019557,10019550,10019547,10048843,10019549,10048843,10019557,10019551,10019547,10048843,10019549,10048843,10019557,10019551,10019547,10019544,10019549,10019544,10019557,10019551,10019547,10019544,10019552,10019544,10019557,10019554,10019547,10019544,10019552,10019544,10019557,10019554,10019547,10019544,10019552,10019544,10019557,10019555,10019547,10019544,10019552,10019544,10019562,10019555,10019547,10048844,10019552,10048844,10019562,10019556,10019547,10048844,10019553,10048844,10019562,10019556,10019547,10048844,10019553,10048844,10019562,10019559,10019547,10048844,10019553,10048844,10019562,10019559,10019547,10019545,10019553,10019545,10019562,10019560,10019547,10019545,10019553,10019545,10019562,10019560,10019547,10019545,10019561,10019545,10019562,10019564,10019547,10019545,10019561,10019545,10019562,10019564,10019547,10019546,10019561,10019546,10019563,10019547,10019546,10019561,10019546,10019563,10019547,10019546,10019561,10019546,10019563,10019547,10019546,10019546,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019563,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019548,10019558,10019558,10019558,10019558,10019558,10019558,10019558</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L23 W21/25; N=173; EHP=23648.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L23 W21/25; N=173; EHP=63884.287972; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10019568,10019579,10019570,10048845,10019578,10019571,10019568,10019579,10019570,10048845,10019578,10019571,10019568,10019579,10019570,10048845,10019578,10019572,10019568,10019579,10019570,10048845,10019578,10019572,10019568,10019579,10019570,10019565,10019578,10019575,10019568,10019579,10019573,10019565,10019578,10019575,10019568,10019579,10019573,10019565,10019578,10019576,10019568,10019579,10019573,10019565,10019578,10019576,10019568,10019579,10019573,10048846,10019578,10019577,10019568,10019579,10019573,10048846,10019583,10019577,10019568,10019579,10019574,10048846,10019583,10019580,10019568,10019579,10019574,10048846,10019583,10019580,10019568,10019579,10019574,10019566,10019583,10019581,10019568,10019579,10019574,10019566,10019583,10019581,10019568,10019579,10019574,10019566,10019583,10019585,10019568,10019579,10019582,10019566,10019583,10019585,10019568,10019579,10019582,10019567,10019583,10019585,10019568,10019579,10019582,10019567,10019584,10019568,10019579,10019582,10019567,10019584,10019568,10019579,10019582,10019567,10019584,10019568,10019579,10019582,10019567,10019584,10019568,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019579,10019579,10019579,10019579,10019579,10019579</t>
+          <t>10019568,10048845,10019570,10048845,10019578,10019571,10019568,10048845,10019570,10048845,10019578,10019571,10019568,10048845,10019570,10048845,10019578,10019572,10019568,10048845,10019570,10048845,10019578,10019572,10019568,10019565,10019570,10019565,10019578,10019575,10019568,10019565,10019573,10019565,10019578,10019575,10019568,10019565,10019573,10019565,10019578,10019576,10019568,10019565,10019573,10019565,10019578,10019576,10019568,10048846,10019573,10048846,10019578,10019577,10019568,10048846,10019573,10048846,10019583,10019577,10019568,10048846,10019574,10048846,10019583,10019580,10019568,10048846,10019574,10048846,10019583,10019580,10019568,10019566,10019574,10019566,10019583,10019581,10019568,10019566,10019574,10019566,10019583,10019581,10019568,10019566,10019574,10019566,10019583,10019585,10019568,10019566,10019582,10019566,10019583,10019585,10019568,10019567,10019582,10019567,10019583,10019585,10019568,10019567,10019582,10019567,10019584,10019568,10019567,10019582,10019567,10019584,10019568,10019567,10019582,10019567,10019584,10019568,10019567,10019582,10019567,10019584,10019568,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019584,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019569,10019579,10019579,10019579,10019579,10019579,10019579,10019579</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L23 W22/25; N=179; EHP=24121.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x6,medium:108x8,medium:123x9,heavy:127x3</t>
+          <t>L23 W22/25; N=179; EHP=65138.312020; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x8,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10019589,10019600,10019591,10048847,10019599,10019592,10019589,10019600,10019591,10048847,10019599,10019592,10019589,10019600,10019591,10048847,10019599,10019593,10019589,10019600,10019591,10048847,10019599,10019593,10019589,10019600,10019591,10048847,10019599,10019596,10019589,10019600,10019594,10019586,10019599,10019596,10019589,10019600,10019594,10019586,10019599,10019596,10019589,10019600,10019594,10019586,10019599,10019597,10019589,10019600,10019594,10019586,10019599,10019597,10019589,10019600,10019594,10048848,10019604,10019597,10019589,10019600,10019594,10048848,10019604,10019598,10019589,10019600,10019595,10048848,10019604,10019598,10019589,10019600,10019595,10048848,10019604,10019601,10019589,10019600,10019595,10048848,10019604,10019601,10019589,10019600,10019595,10019587,10019604,10019602,10019589,10019600,10019595,10019587,10019604,10019602,10019589,10019600,10019595,10019587,10019604,10019606,10019589,10019600,10019603,10019587,10019604,10019606,10019589,10019600,10019603,10019588,10019605,10019589,10019600,10019603,10019588,10019605,10019589,10019600,10019603,10019588,10019605,10019589,10019600,10019603,10019588,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019600,10019600,10019600,10019600,10019600,10019600</t>
+          <t>10019589,10048847,10019591,10048847,10019599,10019592,10019589,10048847,10019591,10048847,10019599,10019592,10019589,10048847,10019591,10048847,10019599,10019593,10019589,10048847,10019591,10048847,10019599,10019593,10019589,10048847,10019591,10048847,10019599,10019596,10019589,10019586,10019594,10019586,10019599,10019596,10019589,10019586,10019594,10019586,10019599,10019596,10019589,10019586,10019594,10019586,10019599,10019597,10019589,10019586,10019594,10019586,10019599,10019597,10019589,10048848,10019594,10048848,10019604,10019597,10019589,10048848,10019594,10048848,10019604,10019598,10019589,10048848,10019595,10048848,10019604,10019598,10019589,10048848,10019595,10048848,10019604,10019601,10019589,10048848,10019595,10048848,10019604,10019601,10019589,10019587,10019595,10019587,10019604,10019602,10019589,10019587,10019595,10019587,10019604,10019602,10019589,10019587,10019595,10019587,10019604,10019606,10019589,10019587,10019603,10019587,10019604,10019606,10019589,10019588,10019603,10019588,10019605,10019589,10019588,10019603,10019588,10019605,10019589,10019588,10019603,10019588,10019605,10019589,10019588,10019603,10019588,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019605,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019590,10019600,10019600,10019600,10019600,10019600,10019600,10019600</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L23 W23/25; N=185; EHP=24604.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x23,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L23 W23/25; N=185; EHP=66450.303156; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x23,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10019610,10019621,10019612,10048849,10019620,10019613,10019610,10019621,10019612,10048849,10019620,10019613,10019610,10019621,10019612,10048849,10019620,10019614,10019610,10019621,10019612,10048849,10019620,10019614,10019610,10019621,10019612,10048849,10019620,10019617,10019610,10019621,10019612,10019607,10019620,10019617,10019610,10019621,10019615,10019607,10019620,10019617,10019610,10019621,10019615,10019607,10019620,10019618,10019610,10019621,10019615,10019607,10019620,10019618,10019610,10019621,10019615,10019607,10019625,10019619,10019610,10019621,10019615,10048850,10019625,10019619,10019610,10019621,10019616,10048850,10019625,10019619,10019610,10019621,10019616,10048850,10019625,10019622,10019610,10019621,10019616,10048850,10019625,10019622,10019610,10019621,10019616,10019608,10019625,10019623,10019610,10019621,10019616,10019608,10019625,10019623,10019610,10019621,10019616,10019608,10019625,10019623,10019610,10019621,10019624,10019608,10019625,10019627,10019610,10019621,10019624,10019608,10019625,10019627,10019610,10019621,10019624,10019609,10019626,10019610,10019621,10019624,10019609,10019626,10019610,10019621,10019624,10019609,10019626,10019610,10019621,10019609,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019621,10019621,10019621,10019621,10019621,10019621,10019621</t>
+          <t>10019610,10048849,10019612,10048849,10019620,10019613,10019610,10048849,10019612,10048849,10019620,10019613,10019610,10048849,10019612,10048849,10019620,10019614,10019610,10048849,10019612,10048849,10019620,10019614,10019610,10048849,10019612,10048849,10019620,10019617,10019610,10019607,10019612,10019607,10019620,10019617,10019610,10019607,10019615,10019607,10019620,10019617,10019610,10019607,10019615,10019607,10019620,10019618,10019610,10019607,10019615,10019607,10019620,10019618,10019610,10019607,10019615,10019607,10019625,10019619,10019610,10048850,10019615,10048850,10019625,10019619,10019610,10048850,10019616,10048850,10019625,10019619,10019610,10048850,10019616,10048850,10019625,10019622,10019610,10048850,10019616,10048850,10019625,10019622,10019610,10019608,10019616,10019608,10019625,10019623,10019610,10019608,10019616,10019608,10019625,10019623,10019610,10019608,10019616,10019608,10019625,10019623,10019610,10019608,10019624,10019608,10019625,10019627,10019610,10019608,10019624,10019608,10019625,10019627,10019610,10019609,10019624,10019609,10019626,10019610,10019609,10019624,10019609,10019626,10019610,10019609,10019624,10019609,10019626,10019610,10019609,10019609,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019626,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019611,10019621,10019621,10019621,10019621,10019621,10019621,10019621,10019621</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L23 W24/25; N=191; EHP=26347.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x53,heavy:86x2,heavy:88x3,fast:98x5,medium:108x10,medium:123x9,heavy:127x2</t>
+          <t>L23 W24/25; N=191; EHP=71166.238859; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x10,medium:123x9,normal:17x23,normal:18x23,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10019631,10019642,10019633,10048851,10019641,10019634,10019649,10019631,10019642,10019633,10048851,10019641,10019634,10019631,10019642,10019633,10048851,10019641,10019635,10019631,10019642,10019633,10048851,10019641,10019635,10019631,10019642,10019633,10019628,10019641,10019638,10019631,10019642,10019633,10019628,10019641,10019638,10019631,10019642,10019636,10019628,10019641,10019639,10019631,10019642,10019636,10019628,10019641,10019639,10019631,10019642,10019636,10019628,10019641,10019640,10019631,10019642,10019636,10048852,10019641,10019640,10019631,10019642,10019636,10048852,10019646,10019640,10019631,10019642,10019636,10048852,10019646,10019643,10019631,10019642,10019637,10048852,10019646,10019643,10019631,10019642,10019637,10048852,10019646,10019643,10019631,10019642,10019637,10019629,10019646,10019644,10019631,10019642,10019637,10019629,10019646,10019644,10019631,10019642,10019637,10019629,10019646,10019644,10019631,10019642,10019645,10019629,10019646,10019648,10019631,10019642,10019645,10019629,10019646,10019648,10019631,10019642,10019645,10019630,10019647,10019631,10019642,10019645,10019630,10019647,10019631,10019642,10019645,10019630,10019647,10019631,10019642,10019645,10019630,10019647,10019632,10019642,10019630,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642</t>
+          <t>10019631,10048851,10019633,10048851,10019641,10019634,10019649,10019631,10048851,10019633,10048851,10019641,10019634,10019631,10048851,10019633,10048851,10019641,10019635,10019631,10048851,10019633,10048851,10019641,10019635,10019631,10019628,10019633,10019628,10019641,10019638,10019631,10019628,10019633,10019628,10019641,10019638,10019631,10019628,10019636,10019628,10019641,10019639,10019631,10019628,10019636,10019628,10019641,10019639,10019631,10019628,10019636,10019628,10019641,10019640,10019631,10048852,10019636,10048852,10019641,10019640,10019631,10048852,10019636,10048852,10019646,10019640,10019631,10048852,10019636,10048852,10019646,10019643,10019631,10048852,10019637,10048852,10019646,10019643,10019631,10048852,10019637,10048852,10019646,10019643,10019631,10019629,10019637,10019629,10019646,10019644,10019631,10019629,10019637,10019629,10019646,10019644,10019631,10019629,10019637,10019629,10019646,10019644,10019631,10019629,10019645,10019629,10019646,10019648,10019631,10019629,10019645,10019629,10019646,10019648,10019631,10019630,10019645,10019630,10019647,10019631,10019630,10019645,10019630,10019647,10019631,10019630,10019645,10019630,10019647,10019631,10019630,10019645,10019630,10019647,10019632,10019630,10019630,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019647,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019632,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642,10019642</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L23 W25/25; N=197; EHP=52584.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x10,swarm:84x55,heavy:86x3,heavy:88x3,fast:98x6,medium:108x9,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L23 W25/25; N=197; EHP=142030.269195; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x10,medium:108x9,medium:123x10,normal:17x23,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L23/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L23/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>236</v>
+        <v>360</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>229</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>215</v>
+        <v>370</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>208</v>
+        <v>310</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>194</v>
+        <v>370</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>187</v>
+        <v>300</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>173</v>
+        <v>290</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>159</v>
+        <v>280</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>152</v>
+        <v>370</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>138</v>
+        <v>260</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>370</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
